--- a/www/ig/fhir/mesures/observations-summary.xlsx
+++ b/www/ig/fhir/mesures/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="83">
   <si>
     <t>Profile</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Indice de Masse Corporelle</t>
   </si>
   <si>
-    <t>null#vital-signs</t>
+    <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
     <t/>
@@ -152,6 +152,60 @@
     <t>null#9279-1</t>
   </si>
   <si>
+    <t>mesures-observation-cholesterol-aspect</t>
+  </si>
+  <si>
+    <t>Cholestérol - aspect</t>
+  </si>
+  <si>
+    <t>LOINC#11158-3</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-hdl</t>
+  </si>
+  <si>
+    <t>Cholestérol - HDL</t>
+  </si>
+  <si>
+    <t>LOINC#2085-9</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-ldl</t>
+  </si>
+  <si>
+    <t>Cholestérol - LDL</t>
+  </si>
+  <si>
+    <t>LOINC#2089-1</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-total</t>
+  </si>
+  <si>
+    <t>Cholestérol - total</t>
+  </si>
+  <si>
+    <t>LOINC#2093-3</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-trigly</t>
+  </si>
+  <si>
+    <t>Cholestérol - triglycerides</t>
+  </si>
+  <si>
+    <t>LOINC#2571-8</t>
+  </si>
+  <si>
     <t>mesures-observation-glucose</t>
   </si>
   <si>
@@ -161,13 +215,25 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS (extensible)</t>
   </si>
   <si>
+    <t>mesures-observation-hb1ac</t>
+  </si>
+  <si>
+    <t>Hémoglobine glyquée (Hb1Ac)</t>
+  </si>
+  <si>
+    <t>null#4548-4</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
+  </si>
+  <si>
     <t>mesures-observation-head-circumference</t>
   </si>
   <si>
     <t>Périmètre Crânien</t>
   </si>
   <si>
-    <t>null#8287-5</t>
+    <t>null#9843-4, null#8287-5</t>
   </si>
   <si>
     <t>mesures-observation-pain-severity</t>
@@ -328,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -759,22 +825,22 @@
         <v>47</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>19</v>
@@ -788,28 +854,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="F14" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>17</v>
-      </c>
       <c r="H14" t="s" s="2">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>19</v>
@@ -823,28 +889,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>19</v>
@@ -858,28 +924,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>19</v>
@@ -893,36 +959,246 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G20" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K17" t="s" s="2">
+      <c r="H20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K23" t="s" s="2">
         <v>14</v>
       </c>
     </row>
